--- a/ai/data/history/CyberJobs_14082026.xlsx
+++ b/ai/data/history/CyberJobs_14082026.xlsx
@@ -513,14 +513,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="67" customWidth="1" min="4" max="4"/>
-    <col width="91" customWidth="1" min="5" max="5"/>
+    <col width="73" customWidth="1" min="4" max="4"/>
+    <col width="236" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -535,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: August 14, 2026 - 12:11 AM | Total Jobs: 40</t>
+          <t>Report Generated: August 14, 2026 - 11:54 PM | Total Jobs: 22</t>
         </is>
       </c>
     </row>
@@ -583,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Staff Engineer - Offensive Security</t>
+          <t>Product Manager, Perimeter &amp; Intrusion Security</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>San Mateo, CA United States</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>7-10 years</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8048657</t>
+          <t>https://job-boards.greenhouse.io/verkada/jobs/5205130007</t>
         </is>
       </c>
     </row>
@@ -618,32 +618,32 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Software Engineer, Cryptography</t>
+          <t>Senior Staff Product Manager, Device Security</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA</t>
+          <t>Remote (United States | Canada)</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-8 yrs)</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8077370?t=gh_src=&amp;gh_jid=8077370</t>
+          <t>https://jobs.ashbyhq.com/1password/99eb8a4c-81e1-413b-822f-dd27598207e0</t>
         </is>
       </c>
     </row>
@@ -653,32 +653,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Synack</t>
+          <t>Paxos</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Technical Account Manager, Federal (Penetration Testing)</t>
+          <t>Product Compliance Manager</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Remote in the Washington, D.C. Metro Area</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Assumed senior-level (seniority filter disabled)</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/synack/jobs/8122123</t>
+          <t>https://jobs.ashbyhq.com/paxos/c042ef9c-efb9-45d3-a0e3-b55ddf491f15</t>
         </is>
       </c>
     </row>
@@ -688,32 +688,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>Chainguard</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Strategy Data Scientist - Compliance</t>
+          <t>Staff Vulnerability Management Engineer</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States - Remote</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-8 yrs)</t>
+          <t>7 years</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://www.bill.com/job?6142609004&amp;gh_jid=6142609004</t>
+          <t>https://job-boards.greenhouse.io/chainguard/jobs/4696736006</t>
         </is>
       </c>
     </row>
@@ -723,32 +723,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Compliance Technology Program Lead</t>
+          <t>Senior Payments Compliance Manager</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>New York, NY, United States of America</t>
+          <t>San Mateo, CA, United States</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>http://block.xyz/careers/jobs/5225220008?gh_jid=5225220008</t>
+          <t>https://careers.roblox.com/jobs/8107208?gh_jid=8107208</t>
         </is>
       </c>
     </row>
@@ -758,32 +758,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Commvault</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Databases and Cyber Resilience</t>
+          <t>Asset Protection - Security Ambassador - Coddingtown Mall Rack</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Santa Rosa, CA</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>5-7 years, 5-7 years</t>
+          <t>Not specified (Assumed 1-8 yrs)</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/commvault/jobs/5231304008</t>
+          <t>https://nordstrom.wd501.myworkdayjobs.com/nordstrom_careers/job/Santa-Rosa-CA/Asset-Protection---Security-Ambassador---Coddingtown-Mall-Rack_R-866428</t>
         </is>
       </c>
     </row>
@@ -793,32 +793,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Blackduck</t>
+          <t>Tyco (Johnson Controls)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Lead Enterprise Account Manager- Security- California</t>
+          <t>Director Security Engineering</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Westford-Massachusetts-United States of America</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Assumed senior-level (seniority filter disabled)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/blackduck/jobs/5253319008</t>
+          <t>https://jci.wd5.myworkdayjobs.com/jci/job/Westford-Massachusetts-United-States-of-America/Director-Security-Engineering_WD30275027-1</t>
         </is>
       </c>
     </row>
@@ -828,32 +828,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Anduril Industries (CA)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Security Engineer, Cloud</t>
+          <t>Security Data Engineer</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Ashville, Ohio, United States; Atlanta, Georgia, United States; Boston, Massachusetts, United States; Costa Mesa, California, United States; Remote; Seattle, Washington, United States; Washington, District of Columbia, United States</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Not specified (Assumed 1-8 yrs)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/vercel/jobs/6102335004</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5159366007?gh_jid=5159366007</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Principal Security Software Engineer, Application Security</t>
+          <t>Senior Backend Engineer, Compliance Engineering</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>San Mateo, CA, United States</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7789332?gh_jid=7789332</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8128860</t>
         </is>
       </c>
     </row>
@@ -898,32 +898,32 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Elastic</t>
+          <t>SpaceX (CA)</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>AI Security - Principal Security Research Engineer I</t>
+          <t>Environmental Engineer, Compliance/Air Programs</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bastrop, TX</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Assumed senior-level (seniority filter disabled)</t>
+          <t>1 years, 3 years</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=8079640&amp;gh_jid=8079640</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8702120002?gh_jid=8702120002</t>
         </is>
       </c>
     </row>
@@ -933,32 +933,32 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Bank Compliance Technology Analyst</t>
+          <t>Staff Offensive Security Engineer</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Bellevue, WA; Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/7837311003</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7460167?t=gh_src=&amp;gh_jid=7460167</t>
         </is>
       </c>
     </row>
@@ -968,32 +968,32 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Product Security Architect</t>
+          <t>Staff Technical Program Manager - Compliance Architecture</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Remote Canada | Remote United States</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/beyondtrust/jobs/7966559</t>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5074405007</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Fastly</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Senior Data Security Architect</t>
+          <t>Staff+ Security Engineer, Risk Engineering</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fastly.com/about/jobs/apply?gh_jid=8089506</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5250052008</t>
         </is>
       </c>
     </row>
@@ -1038,32 +1038,32 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Revolution Medicines</t>
+          <t>Upstart (CA)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Associate Director, Global Healthcare Compliance Operations</t>
+          <t>Senior Security Engineering Manager, Enterprise Security</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Redwood City, California, United States</t>
+          <t>United States | Remote</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>8 years, 3 years</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>https://www.revmed.com/careers-list/?gh_jid=7808430003</t>
+          <t>https://careers.upstart.com/jobs?gh_jid=7875459</t>
         </is>
       </c>
     </row>
@@ -1073,32 +1073,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Anduril Industries (CA)</t>
+          <t>Horizon3.ai</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Product Security Engineer, Programs</t>
+          <t>Staff Defensive Security Software Engineer</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
+          <t>US, Remote</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-8 yrs)</t>
+          <t>4 years, 4 years</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/5041620007?gh_jid=5041620007</t>
+          <t>https://jobs.ashbyhq.com/horizon3ai/95044547-e65e-494f-b04c-ea1853ac1369</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,32 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Security Technical Program Manager</t>
+          <t>Associate Director, Corporate Compliance</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Denver, CO;San Francisco, CA</t>
+          <t>Tempe, Arizona, United States</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>7 years, 5 years</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8068218</t>
+          <t>http://www.hioscar.com/careers/8072656?gh_jid=8072656</t>
         </is>
       </c>
     </row>
@@ -1143,32 +1143,32 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Senior IAM Engineer - FedRAMP</t>
+          <t>Associate Director, Access Management Service Delivery- Cybersecurity</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Assumed senior-level (seniority filter disabled)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7391657?gh_jid=7391657</t>
+          <t>https://biibhr.wd3.myworkdayjobs.com/external/job/Remote-USA/Access-Management-Service-Delivery-Manager_REQ22795</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Sharp HealthCare (CA)</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Staff Security Engineer, Secure Digital Asset Operations</t>
+          <t>Compliance Auditor - SRS</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, United States</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Not specified (Assumed 1-8 yrs)</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>https://ripple.com/careers/all-jobs/job/7836928?gh_jid=7836928</t>
+          <t>https://sharp.wd1.myworkdayjobs.com/external/job/San-Diego-CA/Compliance-Auditor---SRS_JR201690</t>
         </is>
       </c>
     </row>
@@ -1213,22 +1213,22 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Tines</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Product Manager - Compliance, Bridge</t>
+          <t>Senior Security Operations Engineer</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>New York, San Francisco or Remote</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7979422</t>
+          <t>https://job-boards.greenhouse.io/tines/jobs/5973812004</t>
         </is>
       </c>
     </row>
@@ -1248,32 +1248,32 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Senior Product Security Engineer II</t>
+          <t>Security Engineer - Vuln Management (Infra)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>United States - Remote</t>
+          <t>Foster City, CA</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8017071</t>
+          <t>https://jobs.ashbyhq.com/replit/4b290489-9ce6-45f9-bbc8-e1baa4bd8b6f</t>
         </is>
       </c>
     </row>
@@ -1283,32 +1283,32 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Sr. Staff Site Reliability Engineer-Federal, Security Clearance</t>
+          <t>Principal Security Engineer, Infrastructure Security</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Crystal City, Virginia, USA</t>
+          <t>US - Remote</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>Assumed senior-level (seniority filter disabled)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5128580007</t>
+          <t>https://jobs.ashbyhq.com/openai/8f1b8c6b-b414-4026-a434-6ca32c3b3e0d</t>
         </is>
       </c>
     </row>
@@ -1318,662 +1318,32 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Huntress</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Manager, Security Research</t>
+          <t>Security Engineer, Product</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Assumed senior-level (seniority filter disabled)</t>
+          <t>5 years, 2 years</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/huntress/jobs/7808516003</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Chainguard</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>United States - Remote</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-8 yrs)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/chainguard/jobs/4700281006</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Staff+ Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/4502508008</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Compliance, Threat &amp; Risk Assessment Manager</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/8064692?gh_jid=8064692</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Upstart (CA)</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer, Data Security</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>United States | Remote</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.upstart.com/jobs?gh_jid=7767161</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Dragos</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Associate Principal Incident Responder</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/dragos/jobs/5362144008</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Todyl</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Senior Manager, Security Platform Engineering</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Denver, CO; Atlanta, GA; or Remote</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>8 years, 3 years</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/todyl/a37a6cde-3f4d-489b-ac0d-de99218eb351</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Horizon3.ai</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer, Security Controls</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>US, Remote</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/horizon3ai/57d96033-2e76-4f73-87e3-b11e0586ae19</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Inovalon</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>Compliance, Risk and Business Manager</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Bowie, MD</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>https://www.inovalon.com/careers/job/?gh_jid=7815833003</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>SpaceX (CA)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Materials Compliance Engineer (Starlink)</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Bastrop, TX</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>1 years, 3 years</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8484560002?gh_jid=8484560002</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Figma</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Manager, Security Operations</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6015609004?gh_jid=6015609004</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Manager, Product Security</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>5 years, 2 years</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8526680002?gh_jid=8526680002</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Komodo Health</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Senior IAM Engineer</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/komodohealth/jobs/8645586002</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Salesloft</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Manager, Security Engineering &amp; Operations</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>United States, Remote</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>https://www.salesloft.com/company/careers?gh_jid=7890512</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Verkada</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Embedded Linux Security Engineer</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>San Mateo, CA United States</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/verkada/jobs/4129347007</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Oscar Health</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer I, IAM</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>New York, New York, United States</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>4 years</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>http://www.hioscar.com/careers/8059239?gh_jid=8059239</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Abnormal Security</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer, Security &amp; Privacy</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Remote - USA</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>https://abnormal.ai/careers/jobs/7679429003?gh_jid=7679429003</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Staff Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8584366002?gh_jid=8584366002</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Bitgo</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Application Engineer</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>Palo Alto, California, United States</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/bitgo/jobs/8621427002</t>
+          <t>https://jobs.ashbyhq.com/ramp/7c26780b-7923-42d5-8111-9825ff996966</t>
         </is>
       </c>
     </row>
@@ -2001,24 +1371,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
